--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D116495B-9429-4ABC-A236-1502EC0D2BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5419D-F677-45B8-856B-BFB89B44301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="1545" windowWidth="14385" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23490" yWindow="135" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>SelectionNameList</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_100</t>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_101</t>
   </si>
   <si>
     <t>characterDataId</t>
@@ -97,10 +91,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>msgDialogue_Opening_1_1_103</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>character_Minhyeong_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -109,18 +99,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>msgDialogue_Opening_1_1_104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_105</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_106</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>눈감으면 눈물만 나서 오히려 카톡을 보내니까 안정되는거 같아.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -133,11 +111,46 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>msgDialogue_Opening_1_1_107</t>
+    <t>MSGType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>MSGType</t>
+    <t>msgDialogue_Opening_1_1_123</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_124</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_125</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_126</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_127</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_103</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_128</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DateMSG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년 4월 6일 월요일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -171,8 +184,15 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -209,8 +229,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -233,13 +259,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -264,6 +368,34 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,7 +811,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:I1001"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -731,15 +863,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
@@ -747,10 +879,10 @@
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -761,79 +893,80 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="A4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -842,110 +975,120 @@
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
@@ -959,15 +1102,15 @@
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
@@ -1069,15 +1212,15 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -1135,15 +1278,15 @@
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
@@ -1178,7 +1321,17 @@
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+    </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
@@ -2143,6 +2296,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5419D-F677-45B8-856B-BFB89B44301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23490" yWindow="135" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1170" windowWidth="23505" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -8,22 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5419D-F677-45B8-856B-BFB89B44301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC063789-016E-4125-A23A-808648DDE4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1170" windowWidth="23505" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27825" yWindow="1245" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
-  <si>
-    <t>SelectionNameList</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>NextDialogueId</t>
   </si>
@@ -31,21 +41,9 @@
     <t>Id</t>
   </si>
   <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>string[]</t>
-  </si>
-  <si>
-    <t>VoicePath</t>
-  </si>
-  <si>
-    <t>TexturePath</t>
-  </si>
-  <si>
     <t>고유 ID</t>
   </si>
   <si>
@@ -61,16 +59,9 @@
     <t>MyMSG</t>
   </si>
   <si>
-    <t>재미있었지..&lt;np&gt; 잠깐 전화 할래?</t>
-  </si>
-  <si>
     <t>오늘 게임도 재밌었다. 그치?</t>
   </si>
   <si>
-    <t>msgDialogue_Opening_1_1_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>msgDialogue_Opening_1_1_102</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -83,10 +74,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>정말 못해준 것만 기억나는 밤이네. 부족했지만 극복해주고 내 옆에 있어줘서 정말 고마워. 이럴 줄 알았으면 조금이라도 데이트하자고 조를걸 그랬어 ㅋㅋ 내 일상부터 핸드폰, 너는 내 전부고 내 목표고 정말 많은 부분이 차지해있네. &lt;np&gt;너가 어디 막 없어지고 다시는 못보고 이런건 아니지만 나라는 아파트에서 펜트 하우스 주인이 방뺀다고 하니까 시간이 좀 걸리고 씁쓸하기도 해. &lt;np&gt;그래도 뭐 너에게 있어서 나도 소중하고 좋은 사람이었다고 인정받았으니 지나온 내 연애는 열심히 한거 같네. &lt;np&gt;물론 예상 할 수 없는 타이밍에 이별을 맞이하는데.. 어찌보면 내가 선뜻 할 수 없는, 내가 못잡은 타이밍을 너가 용기내서 무릅쓰고 해준거 아니었을까라는 생각이 든다. &lt;np&gt;그래도 나 너 마지막까지 쉽게 안놓았고 잡았다? 억지로 라도 이유 만들어서 너 안놓았다?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>OhterMSG</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -115,42 +102,98 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>msgDialogue_Opening_1_1_123</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_124</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_125</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_126</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_127</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_103</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_128</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>DateMSG</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>msgDialogue_Opening_1_1_100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>2026년 4월 6일 월요일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_103</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_104</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재미있었지..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐 전화 할래?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_106</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_162</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_163</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_164</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_165</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_166</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">너가 어디 막 없어지고 다시는 못보고 이런건 아니지만 나라는 아파트에서 펜트 하우스 주인이 방뺀다고 하니까 시간이 좀 걸리고 씁쓸하기도 해. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그래도 뭐 너에게 있어서 나도 소중하고 좋은 사람이었다고 인정받았으니 지나온 내 연애는 열심히 한거 같네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>물론 예상 할 수 없는 타이밍에 이별을 맞이하는데.. 어찌보면 내가 선뜻 할 수 없는, 내가 못잡은 타이밍을 너가 용기내서 무릅쓰고 해준거 아니었을까라는 생각이 든다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도 나 너 마지막까지 쉽게 안놓았고 잡았다? 억지로 라도 이유 만들어서 너 안놓았다?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정말 못해준 것만 기억나는 밤이네. 부족했지만 극복해주고 내 옆에 있어줘서 정말 고마워. 이럴 줄 알았으면 조금이라도 데이트하자고 조를걸 그랬어 ㅋㅋ 내 일상부터 핸드폰, 너는 내 전부고 내 목표고 정말 많은 부분이 차지해있네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_167</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_168</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_169</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_170</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_171</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -236,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -260,47 +303,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -313,37 +315,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -372,29 +350,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -811,539 +770,459 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:E1006"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
     <col min="2" max="3" width="19.5703125" customWidth="1"/>
     <col min="4" max="4" width="108" customWidth="1"/>
-    <col min="5" max="7" width="77.140625" customWidth="1"/>
-    <col min="8" max="9" width="50.7109375" customWidth="1"/>
+    <col min="5" max="5" width="77.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="C14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="E16" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1">
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2297,6 +2176,11 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC063789-016E-4125-A23A-808648DDE4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127063A5-1065-4D6B-8D66-6A6D18E2ACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27825" yWindow="1245" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
   <si>
     <t>NextDialogueId</t>
   </si>
@@ -53,147 +53,152 @@
     <t>string</t>
   </si>
   <si>
+    <t>MyMSG</t>
+  </si>
+  <si>
+    <t>오늘 게임도 재밌었다. 그치?</t>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_102</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MyMSG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OhterMSG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Minhyeong_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고마워 앞으로도 우리 좋은 사람 되기 위해 열심히 살자 화이팅! 얼른 자자 이제 그만 생각하고…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈감으면 눈물만 나서 오히려 카톡을 보내니까 안정되는거 같아.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>난 좀 얘기하니까 힘든거 같아 미안해…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝까지 아프고 힘들게 해서 미안해. 딱 여기까지만 할게. 고생했어! 잘자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSGType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DateMSG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년 4월 6일 월요일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_103</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_104</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재미있었지..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐 전화 할래?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_106</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_162</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_163</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_164</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_165</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_166</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">너가 어디 막 없어지고 다시는 못보고 이런건 아니지만 나라는 아파트에서 펜트 하우스 주인이 방뺀다고 하니까 시간이 좀 걸리고 씁쓸하기도 해. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그래도 뭐 너에게 있어서 나도 소중하고 좋은 사람이었다고 인정받았으니 지나온 내 연애는 열심히 한거 같네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>물론 예상 할 수 없는 타이밍에 이별을 맞이하는데.. 어찌보면 내가 선뜻 할 수 없는, 내가 못잡은 타이밍을 너가 용기내서 무릅쓰고 해준거 아니었을까라는 생각이 든다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도 나 너 마지막까지 쉽게 안놓았고 잡았다? 억지로 라도 이유 만들어서 너 안놓았다?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정말 못해준 것만 기억나는 밤이네. 부족했지만 극복해주고 내 옆에 있어줘서 정말 고마워. 이럴 줄 알았으면 조금이라도 데이트하자고 조를걸 그랬어 ㅋㅋ 내 일상부터 핸드폰, 너는 내 전부고 내 목표고 정말 많은 부분이 차지해있네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_167</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_168</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_169</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_170</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_171</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>characterDataId</t>
-  </si>
-  <si>
-    <t>MyMSG</t>
-  </si>
-  <si>
-    <t>오늘 게임도 재밌었다. 그치?</t>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_102</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MyMSG</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Player_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OhterMSG</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Minhyeong_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고마워 앞으로도 우리 좋은 사람 되기 위해 열심히 살자 화이팅! 얼른 자자 이제 그만 생각하고…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>눈감으면 눈물만 나서 오히려 카톡을 보내니까 안정되는거 같아.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>난 좀 얘기하니까 힘든거 같아 미안해…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>끝까지 아프고 힘들게 해서 미안해. 딱 여기까지만 할게. 고생했어! 잘자!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MSGType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DateMSG</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026년 4월 6일 월요일</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_103</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_105</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>재미있었지..</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠깐 전화 할래?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_106</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_162</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_163</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_164</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_165</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_166</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Player_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">너가 어디 막 없어지고 다시는 못보고 이런건 아니지만 나라는 아파트에서 펜트 하우스 주인이 방뺀다고 하니까 시간이 좀 걸리고 씁쓸하기도 해. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그래도 뭐 너에게 있어서 나도 소중하고 좋은 사람이었다고 인정받았으니 지나온 내 연애는 열심히 한거 같네. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>물론 예상 할 수 없는 타이밍에 이별을 맞이하는데.. 어찌보면 내가 선뜻 할 수 없는, 내가 못잡은 타이밍을 너가 용기내서 무릅쓰고 해준거 아니었을까라는 생각이 든다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도 나 너 마지막까지 쉽게 안놓았고 잡았다? 억지로 라도 이유 만들어서 너 안놓았다?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">정말 못해준 것만 기억나는 밤이네. 부족했지만 극복해주고 내 옆에 있어줘서 정말 고마워. 이럴 줄 알았으면 조금이라도 데이트하자고 조를걸 그랬어 ㅋㅋ 내 일상부터 핸드폰, 너는 내 전부고 내 목표고 정말 많은 부분이 차지해있네. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_167</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_168</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_169</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_170</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_171</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -774,7 +779,8 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="3" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="108" customWidth="1"/>
     <col min="5" max="5" width="77.140625" customWidth="1"/>
   </cols>
@@ -810,10 +816,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
@@ -824,221 +830,223 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127063A5-1065-4D6B-8D66-6A6D18E2ACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200B7EF2-17E5-410B-8C73-0594895BA195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>NextDialogueId</t>
   </si>
@@ -195,10 +195,6 @@
   </si>
   <si>
     <t>characterDataId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -836,7 +832,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>19</v>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127063A5-1065-4D6B-8D66-6A6D18E2ACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F504204-EFA5-4783-83A5-0C3B89584144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="780" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
   <si>
     <t>NextDialogueId</t>
   </si>
@@ -198,8 +198,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>character_Date</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>BGImagePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Before Sleep Empty</t>
   </si>
 </sst>
 </file>
@@ -284,7 +287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -320,13 +323,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -359,6 +403,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -775,7 +828,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E1006"/>
+  <dimension ref="A1:F1006"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -783,9 +836,10 @@
     <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="108" customWidth="1"/>
     <col min="5" max="5" width="77.140625" customWidth="1"/>
+    <col min="6" max="6" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -793,8 +847,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -810,8 +865,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -827,8 +885,11 @@
       <c r="E3" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F3" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>8</v>
       </c>
@@ -836,7 +897,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>19</v>
@@ -844,8 +905,11 @@
       <c r="E4" s="13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
@@ -861,8 +925,11 @@
       <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F5" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -878,8 +945,11 @@
       <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -895,8 +965,11 @@
       <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -912,8 +985,11 @@
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F8" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
@@ -929,8 +1005,11 @@
       <c r="E9" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
@@ -946,8 +1025,11 @@
       <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
@@ -963,8 +1045,11 @@
       <c r="E11" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F11" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
@@ -980,8 +1065,11 @@
       <c r="E12" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
@@ -997,8 +1085,11 @@
       <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F13" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
@@ -1014,8 +1105,11 @@
       <c r="E14" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F14" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
@@ -1031,8 +1125,11 @@
       <c r="E15" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F15" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1048,113 +1145,131 @@
       <c r="E16" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F16" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F504204-EFA5-4783-83A5-0C3B89584144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="780" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1170" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F504204-EFA5-4783-83A5-0C3B89584144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1170" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F504204-EFA5-4783-83A5-0C3B89584144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1170" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F504204-EFA5-4783-83A5-0C3B89584144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1170" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MSGDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F504204-EFA5-4783-83A5-0C3B89584144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6188AB-A21C-4B7E-8570-A737FB236629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MSGDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="64">
   <si>
     <t>NextDialogueId</t>
   </si>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>고마워 앞으로도 우리 좋은 사람 되기 위해 열심히 살자 화이팅! 얼른 자자 이제 그만 생각하고…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>눈감으면 눈물만 나서 오히려 카톡을 보내니까 안정되는거 같아.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -151,29 +147,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>character_Player_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">너가 어디 막 없어지고 다시는 못보고 이런건 아니지만 나라는 아파트에서 펜트 하우스 주인이 방뺀다고 하니까 시간이 좀 걸리고 씁쓸하기도 해. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그래도 뭐 너에게 있어서 나도 소중하고 좋은 사람이었다고 인정받았으니 지나온 내 연애는 열심히 한거 같네. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>물론 예상 할 수 없는 타이밍에 이별을 맞이하는데.. 어찌보면 내가 선뜻 할 수 없는, 내가 못잡은 타이밍을 너가 용기내서 무릅쓰고 해준거 아니었을까라는 생각이 든다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도 나 너 마지막까지 쉽게 안놓았고 잡았다? 억지로 라도 이유 만들어서 너 안놓았다?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">정말 못해준 것만 기억나는 밤이네. 부족했지만 극복해주고 내 옆에 있어줘서 정말 고마워. 이럴 줄 알았으면 조금이라도 데이트하자고 조를걸 그랬어 ㅋㅋ 내 일상부터 핸드폰, 너는 내 전부고 내 목표고 정말 많은 부분이 차지해있네. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>msgDialogue_Opening_1_1_167</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -203,6 +176,110 @@
   </si>
   <si>
     <t>Sprite/Before Sleep Empty</t>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_162-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">부족했지만 극복해주고 내 옆에 있어줘서 정말 고마워. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_162-2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이럴 줄 알았으면 조금이라도 데이트하자고 조를걸 그랬어 ㅋㅋ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_162-3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정말 못해준 것만 기억나는 밤이네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 내 일상부터 핸드폰, 너는 내 전부고 내 목표고 정말 많은 부분이 차지해있네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_163-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나라는 아파트에서 펜트 하우스 주인이 방뺀다고 하니까</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">너가 어디 막 없어지고 다시는 못보고 이런건 아니지만  </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">시간이 좀 걸리고 씁쓸하기도 해. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_163-2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도 뭐 너에게 있어서 나도 소중하고 좋은 사람이었다고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인정받았으니 지나온 내 연애는 열심히 한거 같네. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_164-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어찌보면 내가 선뜻 할 수 없는, 내가 못잡은 타이밍을</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">물론 예상 할 수 없는 타이밍에 이별을 맞이하는데..  </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너가 용기내서 무릅쓰고 해준거 아니었을까라는 생각이 든다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_165-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_165-2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도 나 너 마지막까지 쉽게 안놓았고 잡았다?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 억지로 라도 이유 만들어서 너 안놓았다?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_166-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_167-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">고마워.. 앞으로도 우리 좋은 사람 되기 위해 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>열심히 살자. 이제 그만 생각하고 얼른 자자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -828,7 +905,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F1006"/>
+  <dimension ref="A1:F1016"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -874,10 +951,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
@@ -886,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
@@ -894,24 +971,24 @@
         <v>8</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>6</v>
@@ -923,15 +1000,15 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
@@ -940,18 +1017,18 @@
         <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>11</v>
@@ -960,18 +1037,18 @@
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>9</v>
@@ -980,18 +1057,18 @@
         <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
@@ -1000,18 +1077,18 @@
         <v>10</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>9</v>
@@ -1020,18 +1097,18 @@
         <v>10</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
@@ -1040,328 +1117,518 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>44</v>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>44</v>
+      <c r="D16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="A22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="A23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="A26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-    </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="53" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="54" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="56" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="57" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="59" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="60" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="61" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -2304,6 +2571,16 @@
     <row r="1004" ht="15.75" customHeight="1"/>
     <row r="1005" ht="15.75" customHeight="1"/>
     <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
